--- a/artfynd/A 36803-2023 artfynd.xlsx
+++ b/artfynd/A 36803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127130851</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127130855</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127130850</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127130848</v>
       </c>
       <c r="B5" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127130854</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36803-2023 artfynd.xlsx
+++ b/artfynd/A 36803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127130851</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127130855</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127130850</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127130848</v>
       </c>
       <c r="B5" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127130854</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36803-2023 artfynd.xlsx
+++ b/artfynd/A 36803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127130851</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127130855</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127130850</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127130848</v>
       </c>
       <c r="B5" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127130854</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36803-2023 artfynd.xlsx
+++ b/artfynd/A 36803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127130851</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127130855</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127130850</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127130848</v>
       </c>
       <c r="B5" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127130854</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36803-2023 artfynd.xlsx
+++ b/artfynd/A 36803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127130851</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127130855</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127130850</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127130854</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36803-2023 artfynd.xlsx
+++ b/artfynd/A 36803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127130851</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127130855</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127130850</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127130848</v>
       </c>
       <c r="B5" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127130854</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36803-2023 artfynd.xlsx
+++ b/artfynd/A 36803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127130851</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127130855</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127130850</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127130848</v>
       </c>
       <c r="B5" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127130854</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36803-2023 artfynd.xlsx
+++ b/artfynd/A 36803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127130851</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127130855</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127130850</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127130848</v>
       </c>
       <c r="B5" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127130854</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36803-2023 artfynd.xlsx
+++ b/artfynd/A 36803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127130851</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127130855</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127130850</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127130848</v>
       </c>
       <c r="B5" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127130854</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36803-2023 artfynd.xlsx
+++ b/artfynd/A 36803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127130851</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127130855</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127130850</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127130848</v>
       </c>
       <c r="B5" t="n">
-        <v>97344</v>
+        <v>97314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127130854</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36803-2023 artfynd.xlsx
+++ b/artfynd/A 36803-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127130851</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127130855</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127130850</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127130848</v>
       </c>
       <c r="B5" t="n">
-        <v>97314</v>
+        <v>97344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127130854</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36803-2023 artfynd.xlsx
+++ b/artfynd/A 36803-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127130851</v>
+        <v>127130850</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>844077</v>
+        <v>844098</v>
       </c>
       <c r="R2" t="n">
-        <v>7376872</v>
+        <v>7376844</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127130855</v>
+        <v>127130851</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>844117</v>
+        <v>844077</v>
       </c>
       <c r="R3" t="n">
-        <v>7376795</v>
+        <v>7376872</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127130850</v>
+        <v>127130853</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>844098</v>
+        <v>844081</v>
       </c>
       <c r="R4" t="n">
-        <v>7376844</v>
+        <v>7376906</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127130848</v>
+        <v>127130854</v>
       </c>
       <c r="B5" t="n">
-        <v>97344</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>844077</v>
+        <v>844076</v>
       </c>
       <c r="R5" t="n">
-        <v>7376876</v>
+        <v>7376857</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127130854</v>
+        <v>127130855</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>844076</v>
+        <v>844117</v>
       </c>
       <c r="R6" t="n">
-        <v>7376857</v>
+        <v>7376795</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1162,6 +1162,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127130848</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flakatjärnmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>844077</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7376876</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36803-2023 artfynd.xlsx
+++ b/artfynd/A 36803-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127130850</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127130854</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127130855</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127130851</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127130853</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,8 +1289,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127130848</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>